--- a/files/data/imagen.xlsx
+++ b/files/data/imagen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yeison Mena\Desktop\vitalixplus-inventario-service\files\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D51C9E3-F49C-49EB-B4EB-A4674873662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540D2349-3627-4F6A-A90A-2910B4DED213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4395" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="imagen" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t>id_imagen</t>
   </si>
@@ -228,6 +228,111 @@
   </si>
   <si>
     <t>https://share.google/images/NY7QQId6eli15Fcxt</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/shopping?q=tbn:ANd9GcRkM43py4E-4oYx04QhwsW92hnWzzLE0OfoJuOr1CdK0XxjAVpt4vXwkP6u8XPkVh_MWOvwjKQl9oe80XBPe6_k2NbF7stXJaZApmnKkInKGYb-aOJ3Ozke</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMQEBUQEBAQDxAVDxAPEA8PFREQEA8QFREXFxcSFRMZHDQgGBsnGxcVITEhKCkrLjAuFx8zODMsQygtLi0BCgoKDg0OGxAQGy0lHyUvLS8xLTAtLSsyLS0tLS0tLS0tLS0rLS0tLS0tKzUrLy0tLTUtLSsrLS0tLS0tLS0tLf/AABEIAOEA4QMBIgACEQEDEQH/xAAbAAEAAgMBAQAAAAAAAAAAAAAABAUCAwYHAf/EAEQQAAEDAgQBCAcDCQgDAAAAAAEAAgMEEQUSITFBBhMiUWFxgZEUMlKSobHBB0JyIzRDYoLC0eHwFTNjorLS4vEWJIP/xAAYAQEAAwEAAAAAAAAAAAAAAAAAAQIDBP/EACcRAQEAAgICAQMDBQAAAAAAAAABAhEDMRIhQQQTUSJhkTJCYqHR/9oADAMBAAIRAxEAPwD3FERAREQEREBERARFBnreDPe/ggmOcBuQO9ajVN7T3KuL7m51Pas2qu1tJnpY6j8F9FUOo/BRQFmAmzSUKhvd3rYDfbVQw1fQwjUGynaNJiLTFPfQ6H5rcpQIiICIiAiIgIiICIiAiIgIiICIiAiIgIi0VkuRhI32HedEESuqbnINh6x6z1KICsTotkMd9eCov0ArY1ZtjW1rENsWrMLMMX0BSjb41bo1rCyaUQymhB718gkvodx8Vsa66j1PRcHeakSkRFKBERAREQEREBERAREQEREBERAREQFBxU9Fv4x8ipyr8Y0Y0/4g+RUXpM7VzlOpfUHHf5qC9TqA9HxKotl0SveLZYi/1r9JjbWYSNzxIa39q/BGzS3A9HNs0QJ5xmgcLvdb9U2HbwVRyg5WMo7lwjDGytgMkzpWNMzmZ+bYI43udZtiTYAX3JBA4Kv+1Sq5x7Yo6WzXObnjzyxuANszXG12ngbDgujj4M8+oyzzmM3XqjaiWzSacgkEubzjDlNjpfjsPe7EfUygm1OSLyAESR6hrbsNj7R07OK8vpvtLrDo5lMT1GOQHyD1jVfaRXfdjgHdFIfm9bX6Hl/b+XJPr+K3Xv8Ah6l6RLf83NswF+cZ6uQG9vxdG3ZdbY5HFrS6PK4tBczM05HEatvxt1rxaT7Uq8cIB/8AM/7lb8ieXFZW4jFBO5gjLZi5jGBly2JxF+O4Wef0vJjLbp1Y5eU3HrELrnwWuuK+0p6R7vqtVc7Vc2PTTFNh9Udw+SzWEI6I7h8lmroEREBERAREQEREBERAREQEREBERAUPF2Xhd2Wd5EFTFrnbdjh1tI8wlTHPsNwFYYf6p/F9FWwbKbSyWB8FlbqLZdPNJ8YqJ62enmw412HTYnJABzbyYZInNgdLHKwdAgNzG9tzYjVa8KoaOkqZqLn2GOtklpY8we9/o5Do48r2tyg+kZxckXETTxVvUfZuySWaX0yojM880z2R2awiSRzspH3gM1tVrP2SUzBf0mcnfoiNv0XdOfi1qX0yuqrMUrQ0QVTnD02oEWHTs+8yWmn5uqlP4skTB2PcpdRiNQJ8ZjhlmBYGmBkb3NyyvmaLsAPRcb2uOtbmfZlSEnNJVuJ3OeIE9941uf8AZLREC01S3sJid+4FafVcFnf+v3n/ADTL7U3tQ1Ucc9KIIZWTy4fW08jixsgc6OV7WVLi5ws+895MwJ6Nl0XJ/BHDHquqlDo/711M1zXDnmuyNfK11rEAEDe/TW6h+zqggOYiSY2taR3RI6i0aEdi6Glghg/uYYobgNJjYxhIHAkDVc/L9VhqzGtelxRnpO8Pqtcwu7vNkwx1w49v0/msohd47/5rDD+lbFYIiLQEREBERAREQEREBERAREQEREBERAREQc2wWJH9aaLfCNbLVILSOH6zv9RW2BwB18FllNxfLpMbEtcx0W6Z1m3UGrtlz3AHEk2CplNTUZVsY9rGklQ5ay5WDI3PGgJHXsPM/RQ6mkyXdJO2MXALYwHOB03c7vF+jxWX2+XP1jNRMxtTQ++pVdW14bsC49Q0Hif+1X1le1pywtdM61+kXEm5sHAk3DdHXsLXsNLqA/ni4F3QaHOJb0SSLdEaDtN9thvuurD6Of3VrjxT5dtyXqHPge5wAPOuAAvYANbx48dVZUnr+aquSotS98jz8h9FbUPreB+YVrJLqIsk3pOREUqCIiAiIgIiICIiAiIgIiICIiAiIgIiIOdqdJ3jtv56qLiUxY1pHtgfAqVXfnLu5v8ApCh4p6rfxX+BWdw8/wBO2mvKaaazFCW5OcbGQAdS3Ob6C19Bc6XIKr6XEmAgNY6aUuc1hOZ5ba1yS83tf2dAsKqCMXdIXODnh4jFhdwjDbC2pFgOPXwVlCQyIvAZFI5ptewGfUtvffU6rpxxwx9RaYyeo+Nq5JWyCVzYYy10Zbrms+IixBGYG/HTVrxrotDaeHncrnSTvyNZd7iNCbO36dxdtwSeJ0Nyp74oySSZJbta0tu6NjrAdJxOuY5W9IAGzQF85qR5sHiFmlxCBmd2PkcCT3gA9qi5yM7yYxrqGBgDWgNbs1rQAB2ABRm4NNKbNZlHtyaAeG5/rUK+w6nZGNG9Li8kvee97tT5q0jKef4PvfhCw3D/AEeARZy8gucXEAXJN9ANh2fE7qVQ+se76rOY6LCh3PcFleze4moiKVRERAREQEREBERAREQEREBERAREQEREHPYj+cn8DfkqjlHWthYHu6yA0bucbANHeSrjEPzk/gb8iuZxOHn8WpITctZFJUOHDcgX923iqXK4+4tcvGbbaDBZH/lZ3lriAcrN2jcNufVHYBfturKKiYw9BlnbF7rvkPe913HxKvnwBYsiG9lEyyn6fhjlu/KldK9rrejPezMQHgONxlFjpqBmEgJsdMpAN0jrpMgPobs7mOdqZQ1rgxxs4c2SLOblPHUG2th0LNDfYfBQZsMic7PeQkknM129ze9/AeQ6lphZfhaTH8IjcUfZxFHKMpBAIkLnsJbfK3IOkAXXBIsRoXKVhlc95IkhdHYOPOHMGkgtsAC0dEh2h36JuAtkFExjs7M99bAkZW3AGgtpoP6sLb3MJVsrJE3XxGx7rtSh3PcFi1lm2vdZUXrHuCzl2tOkxERWQIiICIiAiIgIiICIiAiIgIiICIiAiIgoKz84f2Bo/wAoXO4ZKDjMzj+jo44+4uIf+8r97ryyH/ELfLT6LhKWqLcQqnt1JeW/ssytHyC5+bLxm0ct1I9OfOLaLjOUHLMRyej0bRUVBIbp0o2OJtl09Z3ZsOO1lz3KLlZKQaWndaRw/KSMJvGNbtB4HrPC6k8j8HFOwVDh+Ud6l92sPHvd8rdZVM+S2enPeS31HW4DgjtJ66Q1VSdQHG8MH6rGbX7bK8pqdkbckbQ1uZzg0bAucXGw4ak6KkGLMjbmlkZE32pHBg+KrOUXKinfTOEVTMDzkIdLSiVpa3nm3AmyZRcab63VuK9RtjrqJON4vUx1roI7c2KVkzbhjbnPZzs7jr1W0W7kbi89Q+oE5BZG6FrCG5crizM5uYCz92m/auMmqqJ45z+1cRDsobd8MRlLfYzugva9zbrJUKqdRQsc9mL1zHEC4HNRkkWGzItwAANu9d3huaa6eyvddY0nr+B+iosIrr800uL7xtBe7dx5v1j2lXkZs8d9vMLnxu1cbuJyIiuCIiAiIgIiICIiAiIgIiICIiAiIgLF7rAk7AEnwWSh4tJlid22b57/AAugoqZ/RLz1l5+ZXlWI4m+Fr52WzSxiztbtLywkjt6JXoeNz81h88g3bSzkfi5s2+K80qZBJTMGgPQB3Atq3Ujvv4Ll5vhTm/CXyPw8OJfKR6olne46MjvoCTxcQb9gKtsT5RyTycxRtI65XC1hexIHAdp17FSYc1zmCJhL87wWj25CA0EDqGgHfwuV6VhtBTUMMcNTHFFI8hnPuy/l5CC7IJN779HTQGyph7lvx8scMLl6ig5P8noi7nJiamXi+UkjuykrqsWiAgawN09JpRlaBa3pDNgvMuXVe+gqjFhDp+cbkM4JFRG1zxmDGsdc3ylpN7izhay7LDMVlrsHgqXtbFUPqIY3aWYJWVojDrHYGwNu1b8WHqZuicfjlprq3R87nnD3g5WhzYy25uxvXdoDnt9bz4GNyzqo5cOqHRZMjHujADQ1zXt1sLOIILXHXT+FrSYiG2BfE4nogjMRodyO+3mFX8tam1O8TszRZGvIja8Ai5Fr6C4ttcFbfe/xybTH3raVhTi0wngOa8rD6Ls5OvtBUDDaBpgiNhcwxHUD2ArB6r4eLDjxs2ng3X1aqZ1292i2qywiIgIiICIiAiIgIiICIiAiIgIiICqccf6re9x+Q+qtlR4mbyO7A0fC/wBVFTj25Tlu/LhM562Mb70rG/IryemnLoshcAMpBJOwOlx4le0Y3hQrKR9OXmPOG2eBezmvDhccRcC68vxrk46kkjjdbK5pflGYjOLB5BO42Pjt148uG8fKKcuNvuLTktiE/OtNNAySbIGh0l8rTbpPDQdOOpOlz1rssUw6tnh/9o0EjR0spEhynUXF2kXsSNuKm8h8M9Gpw/KOclAe4kahn3W+Wvj2K+e2/rWIvsdR5KeLi/Tu/KuOHp4fjGHPilEjRJSygDLLFocrQRlyepIy27bA2AuusqJqd1MJWOlsXxFzg18TyWPBBzsGR5B6Qacuw1Xd1+ERzsLJY2uYRtsR1EEagg6gjULgaaJ+EVfNylz6KYgmQ7WvYSOA0D2EjNwINx1C2Ny4vn0buF/ZS09FnIMFbHLZ13RPkbG5mtyQARcX6hx3Uzlrh9XUwNZE9zWWFxJa2U8dHOI002Gy76v5JU8wN4oTIR0ZXxRylrvas4aqlqeSFZYAYhkjY3KyOKLm2hotpkDsuw6tLBdXltt5OwwhhbTwtLibQRNJ03DAL7KQ9cZR0IwsGT0iprah7MrabTIXOsdWgE3uN99TpqunwuSV0EbqhoZOWAytbazXnXKLHhtuVnnPWyS9rCjdqR2XUtVsDrPHfbzVkqRFERFKBERAREQEREBERAREQEREBERAXP4hKOee2+vR0/YC6BcNypcW1TiDboMcPK30UzHfpbHtYx7eJ+aTRNeLPaHC9wCL2PWOoqvwvEA9tnaOBPcVZAqlllXfKZ8sZPTEkduix4yvZ2B40I7CL9qliocRcMHaHOAI8gQfNRwtrCp8qixuFQWi/NSdzcjj8HKoxOZlTG6F9JV31LHOhu1r7EZr32sSCOIJHFT56iVubm489mnJ2usN9RpvpxssaermMga6MBhe8F2V46IFxqTYd+x2G11be57V1Gqklnip442QOkeyNrLyPawdEWBJOp0trxUWKir53E1VRDBFfSCja4uI/Wlfrfu0XRBZtCTPU1CeukejpGRDoNsbWzHVx8VnKVtKr6yrANhqfgq+6me22OQB7e17R8VcLmaR15mXOucHyBK6ZWuPijKaERFCoiIgIiICIiAiIgIiICIiAiIgLh+XbCJ2O9qLL7rj/uC7hcry+hvHFJ1SOZ7zb/uq2Ha2PbksPl6RCuIalw2PgucLsrgVYwTG++i2sl7artuIEbgLazEx1Kqe64WklV+3iadHHiY6vitwxIdS5yNbgo+3Eai+/tPsCDEHHYKkaVKhfZT9uGonumcdyoNTJYrXPUaqMHXVpNJWWBkuqGX4B7v8pH1XWrmeS8d5Xu9lgb4uP/FdMss+2WfYiIqKiIiAiIgIiICIiAiIgIiICIiAqnlVT85SSdbWiQfsHMfgCrZYvaCCCLgggjrBUwjyCRtws6aS47QuxqORLf0c5aODXtzW7LghV0nIudrrskieOIJcw/K3xW3nG3lFW16yabqz/wDGKn2Ge+Fmzk3UD7jffA0U+UNxXMkPALaJiNx4hWLeT9QP0TPf/msxgc/GJnvj+KeUNxBDl95xTmYBOBbI219BmGy+jAZ/ZHvNTyhuKyR6B1lax8m5ibkxt8XE/AKTHyXP3ph3Nb9Sfoo8oeUS+SsdonP9p58mgD53V0tNJTNiY2Nt8rRYX3PEk+K3LG3dZW7oiIoQIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiIP/Z</t>
+  </si>
+  <si>
+    <t>https://www.loanatural.com/wp-content/uploads/2025/07/Activador-de-Color-10-90g-LOA.png</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMSEhUSExMVEBUVFxgYFxUWFRcXFRUVFRUWFxgXGBUdHiogGBomGxcVITEhJS0rLi4uGB8zODMuOi0tLisBCgoKDg0OGxAQGi4lICUtLS0tKysvLS0tLS0tKzAtLS0tLS8tLS4tLS0tLS0tLS0tLS0tKystLS0tKy0tKy0rLf/AABEIAPgAywMBIgACEQEDEQH/xAAcAAABBQEBAQAAAAAAAAAAAAAAAwQFBgcCAQj/xABMEAACAQMCAgYFCAUICQUBAAABAgMABBESIQUxBgcTIkFRMjVhcYEUI3N0kbGywjNCYqHRFRdSVHKDwdIkY4KSk6Kj4vEWQ1Ph8DT/xAAYAQEBAQEBAAAAAAAAAAAAAAAAAQIDBP/EACYRAQEAAgEDBAEFAQAAAAAAAAABAjERAxIhEzJBUXEiUmGBkUL/2gAMAwEAAhEDEQA/ANxoorwmg9ornWKNYoOqK51ijWKDqiudYo1ig6ornWKNYoOqK51ijWKDqiudYr0MDQe0UUUBRRUZ0i47BZQtPO2lBsAN2djyVV8WP/3yoJOisTveuycsextY0Tw7R2ZyPbpwAfZv76R/npvP6vb/APU/zV09LJO6NyorDf56bv8Aq1v9sn8a8/nqu/6vb/bJ/GnpZHdG50Vhn89N5/V7f/qf5qtHQ3raiupFguYxayOcI4bVEzHkpJAKMTsM5HtyQKl6eUOY0uiiisKKSkNK1Vun9/fQQxvYxLM+vDqyFyEKsdQUMpO4A2zzqyc3hLeFi1V6GrELzrO4rCcSwwwnykt5U/E4pu3W5xAAnFscDP6J/D+8rrOhlXP1cW9g17istl6V8TVpE7SzYoWUaYZCNaI0rhiJDoHZo2NWCSRy3pxJx7iwLASWJCZLHspNgO1Gf0hzl41XbxlXONwMdn8t97StNeYrJbzpnxdFUgWrlp+wCiGXOrtJ4w3p+iTATn9oU4s+lHF5ZpYVazBiMPeMMoV0myRIvf8ARCqzHPkRV9Kp3xqOa8Zqyw9LOLGVIVNozMuot2LhEJjDqrt2h0k8twOR5123SfipiMqNaSDBKJ2Equ+limNDSAqS6kDY81OwOQ9O/Z3tO1VyWrMZek/FgxQG0d9REYEMumUKsLFg+vA/TKADzKsKhuM9ZXEraZom+StpwQ4ik0urKGVhmTOCCPduKs6VukvUkbPqrlmrEbbrS4nIcRxwSnySCRz9iuatnRPjvGbi4iWe2jhgJJkdoWjYKFJwoaTOScDkedL0rNrOpLppgooork2KznrG4VHeXEccpfTEuVVW0jU/NiMbnAA+3zrRq+f+vBj/ACmPq0X45q3hOb4SrPw7qysH9LtvhLj8tSjdUfDgM5n/AOMP8tYI7kAnJ2HmauXFOiKRtdBZpMW9lFdDVgl2k5oSMYXy8a63HKf9M+FxvurWxQ7dsPfL/wBtK2nVjYNz7f8A4o/y1l/SHh6wC00Mx7eyguH1HOHlMgYL5L3BURk+Z+01Zjl9nMb0nVFw0+M4/vh/lprfdVPD1Bx25/vf+2sQ1HzP2mvCT5n7TTsy+zmPrHgjkwJkliBpJPNtBK5J8zjNPqq/Vh6rtPo/zNVorz3xWxTXiK5QnyINOq5kXII8xj7agbwAOuGAYeRGR9lR990SsZv0lpAx8+zUN/vAA054a/hUjVlsThUrjq44e2r5uRC3pFJ5l1ePeGvDb+dR83VRZnZZrqPnymB5nUfSU/rb+/er7RWu/L7Ttn0zr+aWIbi+vRsB6achnA9HkMn7TSSdT8K8ry6XYDYoNhnA2XkMn7TWlVxLMqjLMFHmSAP31fVy+07MWefzSQkYa9vGGMY1pjHljRy9lO4uqu0B1NNdyNzyZ8HOMZyoBzjb3VYrrpRaR+lKD/ZDN+8DFNYum1mxwHY/3b/wp35/a9mJtadXPD41CiKQqP1TPMVyDkd3XjnvyqSs+idjFjRaQAgYBMasQByAJycU/s+JxS+g4Ps5H7DvTusXK35XiEOzVFwqhB5AAD91I2QyzH/9vSt021c8PHdz5k/wqKdUUUUBXz/14esx9Wi/HNX0BWAdeHrMfVovxzV16XuZy0z6Tkc+RrU+NdJeI2rCEWlvdhoIsyiylbWjICEYhzqxt/AVljjY+6tg4qvHJWjezZ7eDsYgqGW25hAC2CTzrrn8csxnPSvi891Mj3EK2zJEsaxrE8SiNWcrhGPmzDbbaoap/ptBfJcKOIsXm7JSpJRvmtcmkZTb0tftqArWOkoooorQ+l+rD1VafR/marRVX6sfVVp9F+ZqtFeLLddYKKKKgjYhplYe3P271JUwutpAfMfdRf3LAoqFVLFixYFgsaKSWCgjPeKDn+tQP6j+M8bt7RO0nlWJfNjzPkBzJ9gqoHpyLm1upbG5hke2haVhJazRjTpYghmcD9VvPl4c6yCfg3FL7/SngubnWARIUOCp3BQYA0nmNIwa64dPndYyy40vvSLrlG6WcRPP5yXuj3hBuR7yprOuKdK7y4OZJ39ynQP+Xc/GpHo10dje04hdXCP/AKMoSNMsjfKWyNLLz2JjGn9qot+i18qdo1ncqoGSTC4wPMrjIHtIrvjMJfDnblUY8hbmS3vJP314jEbgke0HFO7ThNzKoeK3nlVjpDJDI6lhzAZQRmuLvh80UnYyQyRy7YjZGDnPLC4y2fZzrfhnyluBdMru1YFX7ZBzjlywI9jekp9xx7DW89CulEd9CJEJ/osrelG4AJRvPYgg+II+Hzrf8EuoAhmt5oRIQqa4nXUx5KMj0j/R51ofVJw67troiaCWCOZFwZEZQzo4IG/JtJk2O+AfKuPVxxs5dMLeWwXrU4tlwi+776Z3pycVIAV5nV7RRRQFYB14esx9Wi/HNW/1gHXh6zH1aL8c1del7mctM/Y1pnBoOFWsKPBfQC8IBNxcQPL2JI5QxDCqRk946j76zNq1ror0f4cwga0ig4rIxj7cXFwFkgUsutltCgVgo1Hffu7Zrr1NMxnfShR2+oXv8pl1DNPpde9qYFMMTywDtt3sAbVEirJ1i3M738onj7Lsy0cK9n2Y+TJLJ2RUfrA5Y6vHJ8sCt1rHSXYooorSPpfqx9VWn0X5jVoqr9WPqq0+i/MatFeLLddYKKKKimPEx6J9pH2/+KrvS3jK28NxcGP5R2caQiM5Ad5yC67AnGgxEnHIVZuJL3M+RH34/wAazrrI4jeWkXbWkzwjWpkwsbd1lKau+px3ggrWM5vCXSMktDecLSOG2XgzXF2kYhQALdJsS7ZVXKqO0bHiITzBGHPReK2TiKWCXXFZpbbmWmCWgEAGU7LIPZ+iuMEbjfG9ZzDxe8vruAyXb9orZSViAsOkF2cIoCjCqScDcDBqyjjPGnRxJfaMXQsyOyh1MzSGJ2DCMHQG2zzO+ORrvcLPHLnL8rVPw1r6CONJBbm9upr6SRRlvk0DhYWUeLEfJCDy5n2U36JcatQt5dQ3fE7gWsDFvlk2qBywYqVTnqyniBjV7aq0I4ktxiO7dZbS30RB7dYNUfapEsEaldLhmCgFuZA3qM6T9KuISRrBPc9pHPFHKyCKJMh+8FYhAcjA8akw58L3JvpFeXNlY8N4fayvBLPGZJOzbS5kuHGhdQ3Ua3fljlVw6U3RhW/vYQZLmzigtEcqHaPVpkllGQd9NwCSdvm99s1jl50guZbhLqSXXNHo0OUQaezOUwgXTsTnlT3hHSviEdw8sEztNcMDIoRX7Zhy+b04yP2QMD2Vq9Os962dV19JPJdXV1PcXHySHtI1ZmmKPIJA0scbEjUFRgMf0iKuXQeeERM63dzcrMyy5vJYtUaxuNThNWpFJx4Y9H2Un0L6J3rTniPEJ3Sdo+zWKPSumPmBJpGk4O+nffck+F2m4VG6lZczAgqdZGMEgkYUAc1H2VxzynPh0xnhy2C6+OSDt9tSNR1tGA6qBgKMAeQAwBUjXNoUUUUBWAdeHrMfVovxzVv9fP8A14+sx9Wi/HNXXpe5nLTP2bAJ8q0GLoRYgiKW7niuYrYXkzCNWiSIAO4j21dooIwcn3eFZ7INj7q3C1N0yiQ2XCnZ4FiZ3uTreEoBof5vkQBkV16ls0ziyrpZdwySp2Fzc3iLEq9pdfpAdch0DIB0AMMZzuT4YqGqy9YFqYrlFNva2vzSnRaPriPfkGonSO+cYIxyVag+H8OmnbRBFJM3kilse045D2mtY6Sm1FWDjvQ+5soVlueziLsAsPaBpsEMdRUZAUYxz8ar9WXnQ+l+rH1VafRfmNWiqv1Y+qrT6L8xq0V48t10goooqKSulyje77qibiwWeMqwDZBBDDKspGCpHkamiKj7M4OKDJeNdWjwSNLZyBCVkXsps4USxPE2iUb+i7YyNjjc1X7yPikbhniWQqbcgjSwzaMzxkgNk5Z3ZjzYseVfQ1wyhSz6QoGSWxgD25qMa3tJNyiHdRuhU5c4XYgczXSdW/LPZHzpMlziQLbLb9qF19msi5KSCUNlnYhtSrv7PjTq44Vf8Ql7VowzlVUkYUEIunOkE7nmfaTX0DJw6yjzqihXSFJJQHAYlVJJHiQRT4SxR9waUxp2AwBrbSuw8zkVr1vqJ2Ma4B1PTSYa5l7JfFUHeP8AtNy/3a1Lo30RtLFcQRBWIwZD3pG97nf4cqk5OIRq2gsNQIB2JwW5AkbAnbnS3brr7PUNenVp8dOcZ92axlnlltZjIUrxuVcxSqwJU5wSp96kgj4EGvZOVYaNLUd8+6ntNLMbsfd/jTugKKKKAr5/68fWY+rRfjmr6Ar5/wCvH1mPq0X45q69L3M5aZ+x2Na2/RaAq1kvDAyfIe1W+7NjK1z2YcDXpwcsfRz7MY2rJHOASfAVq9vDNFN2MvErzTa2hubzQ+AmFQxwwk+ak7nOdO2PDr1GcWX3fDZLchJYngYgNpdChIJIzgjlkEZ9hq4dEOmb21sbR7aWWBmZjJbySRTqW54ddm92RUf09QmWCcTTXEVxbrJEbggzRqXfMTEbHS2Tn9rx5mzdXXGOIR2vZxWyPbdox7dp1t9LH0hrbIbHlpplecSbRHT6S1uI4LmCWYNHHHbGG4iZZNKdowkMp2c74OM+BqlVo/WXxBZIEX+UJLlu0Ba3+bkjTCsNQnSJMkZxg+ZrOKuGi7fS/Vj6qtPovzGrRVX6sfVVp9F+ZqtFeXLddIKKKKgKjV2cj21JVHTjEh+H3UCvEbcugC4JVkcA8m0OGwT4Zxz8Dg0hdmWRP0RUq8TBSyamCSBm5HA2HnvUjGdqjb3hZdmYMASRjIBGAE5jG+68uW5oOLy0eQsdGAywDSSD6EzM4O+PRNIHhcgZwO8uYAhJ30RzFyDnxUHGfEY8adDhxJ3C+1iSzEadOg5G6g+Ps5Z3rleGEFsBCCVOk7BgqBdJ7uQM7+I9lApbLJEWQR9orOzBwyjAdtRDA75GcDGcgDlTZ7KbtO2yuRJkJjvdkB2enXqxjSS+MelS03DCSSulCdPLPhG64yMbZYfAUPw1iDpKxnvaVUkoCVUeQyDg52HPPPegW4WjprVkIHaSMGypBDyMw2ByNjTublSlJXB2oE7Ic/fTmm9l6PxpxQFFFFAVgHXj6zH1eL8c1b/WAdePrMfVovxzV16XuZy0z5+R8dq1d47y5tRb/KeEa5kiR5RORczxx7pE+F3PgceZ86ylq0nhnHOD2tuEt557SZlHa3It+0nJwMqkjDEa5z6IHnz3rtmzEB1mQXEd4sdwIEKwRiOK2LdjDCGcLGMgEHIY8uTD3CW6KTX0drZrbXhgW6upIQnYxusbAZL5Iy2fLaqp0ms4o5h2MlxMsiCQyXMbRyOzM4LDUAXXCjvb5Oryq59X95eG1Ag4bHepbStIkryhGWVgCRGDzYDHLzqX2nyjekHELu54fJJc3TTCG+NuI+zjVSUjY9plVBzuRjlvVJrQum73YsgJeGR8Nhe4WUssilpJWRxug3BI55xyFZ7Vw0V9L9WPqq0+i/M1Wiqv1Y+qrT6L8zVaK8uW63BRRRUUUwvh3wfZ/jT+mfER6JoHEJ2pSkbY7UtQcTJqBGSufEYyPaMgioe94C8jRsLy6j0NqIR0Afl3W7m4pe+4/DC7I5YMoDEBGbZmVdsDc5ZdvbXM3SGFdROsqobvCNyrFF1OqtjDMFBOB/RbxBxZyng8tLUoTmWSTPg5XA92FFOqiB0hhJIAkLKyroEbFyzKWwFG+ygkk7DFdf8AqCHJB7QEErpMb6mZTGuFGMneVPtPkacU5StNrw7Uzi6Q27MV1kOACUZWVwDIYvRIzkOpB94PIglhxPpPbLdCyMh7c47uhyo1AsAXxpBIGcE+IpxTmJyx9AfH76cUhZegvupeooooooCsA68fWY+rRfjmrf6wDrx9Zj6tF+OauvS9zOWmft7K1zojdcMHyf5CbOKfVH23y1X7cjUvaCCRjp1EasBcjlyrInbAJ8q0dejPC1JtpluTLDZC9nmRxpkRVDvEsZ2UYbY7H2+J7Z8ceWcVf6yflX8oTfK9WoljDkoR8l7WXsdOnbTjVz3znNTHRm7smtLOOe+FnJbXjXGgxSOZAGUgZUgLkAjO/PlVT4/d2sjp8kjmihSMKFmk7Rgwd2Ok6iFTDLhRjfJxvVl4fZStwVvkcPbyS3DLdlE7SdY00tCoUd4IcA7A8z5mpZ+mSnyZ9OIrV5JbmHiQvWlnZuw7KRTGrlm9NmIOkaV5DnVUq78ctZBwiE3kAt5o5xFbFk7OZ7cRksHU97SDyJA5DzyaRWsdFfS/Vj6qtPovzNVoqr9WPqq0+i/M1WivJlutwUUUVFFNeIDu/H+NOqa8TbEbHc4wdgSeY8AMmg6tDtTioez4imOe/lg6tlDbL6R+ypJJwfhkfYcUDW+4LBNr7RA/aaNWfERkFRnyBGaZ8SsbWGNpJ5Ozi72TJLpjDSqUZtyAGYMfixI3JzI8Q4hHCheRtI5DzZjyVR4k+VYL016VfLrwCU4to20qg3Cnk0n7Te3yBxzrphhctMZZTFt1vw2CQdrFIWDMJFeOTIDaSuVYbEFSRg5FKy8FiY6iGDZJDB2BDExnUD55iT945EiqZwLib8PiW1itZ7192HZaRGsbAFC0jHCgggDz0nypxccd4q//ALVlYj/WyPcP9kYAz76nbV5Wf/05bnOVLElGLFmLa45HkV9Wdjqkf2YOn0dqYcW4Dbm6W8KEzKuAdR08iobRy1hSRq8j7BivLDfyt85xSVAeQgs441+DuSa64j0ZyuW4lfykj9W4C8xtsi4FNfJ/S/2g7i+4fdStJWselFXc4UDJOTsANz4mlaw0KKKKArAOvD1mPq0X45q3+sA68PWY+rRfjmrr0vczlpn0nI+41rHF+O8XtnWOG3jukMEXzq2ErZV4xlCyudWOR+6sncbH3Vr3FLLjE5je1nFvF2MQEfytRusYBOANs11z+GcWd9LL65mmV7qEW0nZhQghaAFAzkNobc7lhq9nsphw7iM1u2uCWSBjsTG7ISByDYPeHsNSfTO1vI7hVvZe3l7JSG7TtMR63AGr+0HOPbUFW5pDjiHEJp31zSyTtyDSOzkDyGTsPYKb14K9qj6X6sfVVp9F+ZqtFVfqx9VWn0X5mq0V4st11goooqAptxOPVFIpGcqdiAfDyOxpzXEy5UjlkEfaKCotcQ2ya7qVIE8nYYY6SpAQABsg+R+6mNv0tnuNuHWUtwp5XFwTBABjmue83h6IFc8A6Exq/aMO2k8Z7g9tKT+yD3U+AzV7t7cL4knzJrduP5ZkrE+mvFLkdpLcHEodreCMd0Rrg65wvPLgHSfIjfY0wu+k3D2XSLDGW37sa5UxaMZU5XB5AeQOc1vV5ZRyqUlRZFPgwBH76q1/0ChJ1Qu0X7DHWnwLZZf3+6t49SSaZuFVzql42JxLC470ajQT4wK7lV8u5rK+4qKvkxCH0VHgDgDOSV5kgc9P6362Mcs1YdH7i2bt4wNUKyEYQsHyhAUqrlnGdJwAM6R5YKI6S3+T8wfMH5DcjO5597n3VPuOKzlObzFl4nFT1zcHIJzGNsDdCd4io3Cb5YrjV7P6QVndvkDALYxg4ZhtrYbgvtjSfcVPitRS9Ir9dhbeeNNncqDgbZXI8EjHxxy5t5OI3jzRf6MrZmQEtZzIVjMid/WeR2Lc9iAfYEhy1AV7RRXNsUUUUBWAdePrMfV4vxzVv9YB14+sx9Xi/HNXXpe5nLTPZTsfcfurSulfRrhjTI0t7HZOYIMxC1LAfNjvalwCTzrN2G1aVwezseIjtpbe90xoqy3c1zGlugQacaydwMYwAT512y+2Yo3HeH28EgS1uBdoUDGQRmPDlmBTSeeAFOf2qjqmelq2S3GmwLtAFALPnLSam1Fc76MaMZA8ah61NJXlBr2vKqPpfqx9VWn0X5jVoqr9WPqq0+i/MatFeLLddYKKKKiiiiigjeH86kqikDB204O7bHI33xuPbinzGTw0fHPsx/j+6gXrmVsAkDUfLz9lIydrgadGf1s5x8KZvaykklYife/P/wAUCtw5kQqUkTPMqVyMHPn7PvqHj4CMhhNe7HUPnhjljceI2zg/41K/ImwcrHy7uC43AwuTzIxXgs5AMBYvYMvjOQTv/sig4kh1Fie2XmQNeBy8PIb0hBHpkVcyHl6ZB5Ypw1nJv3Yt/DMg21Z50laxsJFBCDn6OffzNBNUUUUBRRRQFYB14+sx9Wi/HNW/18/9eHrMfVovxzV16XuZy0oBGa07hPHeI38cUKcKtbqKIKFaWE9kuBjUGdgudt9OTWYsMjFaHYdZKSCBL6CQi3aMo9tM6fomUrrgLaJPRGcn3Cu2c+ozEB1gQGO6VGWzjdYVDpZDESP2kuVb/WjbPLbTVcqX6Xm2a6eW1maeOctMdSFGjkllkZoyDzxsc+TCoerjpKKKKK0Ppfqx9VWn0X5jVoqr9WPqq0+i/M1WivFluusFFFFQFFFFAxj/AEje+n1RzL84cbHNPA7DmM+7+FArRSIuB45HvB++uu3XzoFKKS+UL5/uNcm58lY/DH30CzVHI3zq/H7jTl2cjfC+7c/bTK1Hzi/H7jQS1FFFAUUUUBXz/wBdwJ4qqgFibeEAAEkkyTYAA3J9gr6ArOunnSez4bdGbsRcXzxKq+GiIF8Euc6FLFvRGpsb7DI307ZfCVRejnVLe3ADzlbJDvhhrmI+jBAX/aOR5VMXHRjgNnlZ7n5RIvMNOWYH6KDBHuIqrzX/ABfjbFVEksecFIvmrVfMMxIDe5mY+VTvDOpacgGe5ih/ZiRpdv7RKAH4Gu1v7r/jP4IS8U4ED3YVI+ryn97DNKRycAm7rBYT54uIR/vDC/bUx/M5bDndXBPsEQH2FD99Mrzqijx83dyKf9ZGjj/lK1nnH7q+XMnVbb3KGSwvAw8mZJY/d2ke6fEMaoXSLozdWLabmIxgnCyDvROf2XG2fYcH2VOXnQC/tH7W3cSMvJ4HaOYfA4+wMal+B9Z0qBrTisPyqI91y0YEyg//ACREASD4Btv1jWpb8XlPDTurD1VafR/marRUT0VhgS0iW2YNBpJiIJI7NmLKMtucA4332qWrz3bYoooqAooooGR/SH4fcKeCmjD5w/D7qeUHmKNIr2ig8xRivaKBOblUfafpB8fup/cHamNl+k+BoJOiiigKKKKAqn8c6BW95fi7uSZVWJIxByQlHkbU55sO+Bp2GxznlVwqL49ePFDNJEhlkSNmRACS7hTpUAbnJxVls0HiGKFVQaIlAwqjSigeSryA91duKw/o31YT8RWW54hLNDMWIXtI8uxwDrYPyTJwFXHI8qedSnFZ0u5+Hs5kiRJGAySsbwypGdHkjauXLYeZrdwnF4qctZnGBk4A8zsPtpm6gjI3HmNx9tZDd2E3HOLzQzPJFbwmXQNJKrHC4jGhT3dbkhtRzzPMACmvELKTgHEYkhlaSGQIzKcDXGzlHV0HdLDTkMMeHty9P+fJy1yaOq/x/gMF0umZAx/VcbOv9lufw5eyrNfMsYZnZUVebMQqj3k7CoxrmNtOmRG1DK6XU6hvuMHcbHceVc/M8qneh9gLeyt4Q2sRxhQxGCQOWR51MU04SPmU/s07oCiiigKKKKBpJ+k+Ap3TWYd8HzH3GnINB7RRRQFFFFAjcnamVh+kPuP+FO7s7U24am5b4fGgkaKKKAooooCo68lCuckAYG5OB9tSNVXplw8XMc1sTpEsWnOM4J3U48cMAfhQN+mnCLu9iQWV4LbTr14dgJAwUBdabrjB+2qF1NX3yW+m4fLEiyuXXtB6YeDJMRPIpgOwIxuPHIwy6N8X4pwdHtRYtOpYsuI5HRWIAJR4wQynAODg+6p/qs6JXRvH4neqYmOsorDS7STek5TmihSwAO/e9m/bjjGy6Z2u/TXplb8OjBlJeRh83CpGt8eJ/op5sfhk7Vl/Rrgd3xq9HEbtezt1KkbEK6xklIYgdymc6nPPJ89o7jvA+Jz38t3JYSXAMrFUkQmMxISI0KhgSoXBx4nOeZq0x9KekHdX+TUCjAwIXAC8tvndtqsnE8BbrLjWXiHDLef/APmkeRnBOFaQaQoY+8qP7w1GNwy3t+PQx26rGvYMzRr6KOUlyAP1cgKce3PjVx6y7JpIol/k8cSi1kyKshSeLlhosbnI1A4Pl4cqr0U6Ov8AL0uI7KTh1tDEyqsxzNLI+oFmySTs3M8go9wzL+ka3w0fNJ7qc0hYj5tfdS9cmhRRRQFFFFBy6ZpBiy+GR5inNFA2W6Fd/KBSjRg8wDSZtV8vvoPPlArhroV2LRfL95pRIlHIAUDUoz/sjzP+Ap1FGFGByruigKKKKAooooCorjVoTiRRnGxHjjz++pWigrtrNUrBJXc1gjHOMHzG1cpZ45N9oqB0pr0ik0QilKoSdabGHUaela9AoBVwAB4V7RRQFFFFAUUUUBRRRQFFFFAUUUUBRRRQFFFFAUUUUBRRRQFFFFAUUUUBRRRQFFFFB//Z</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxMSEBUSEhIVFRUXFRUYFRgVFRIYFRUVFxUXFxcXFxUYHSggGBolHRcXITEhJSkrLi4uFx8zODMtNygtLisBCgoKDg0OGBAQFzElHR0tLS0tLS0rLSstLSstLSstLS0tKystLSsrKy0tKy0tLS0tLS0tLS03Ky03LS0tNzcrLf/AABEIAOEA4QMBIgACEQEDEQH/xAAcAAEAAgMBAQEAAAAAAAAAAAAAAQIDBgcFBAj/xABBEAACAQIBBgsDCgUFAAAAAAAAAQIDEQQFBhIhMXEHIkFRUoGRobHB0WGSsiMyQkNiY3KiwuETJDNTghY0g+Lw/8QAGQEBAAMBAQAAAAAAAAAAAAAAAAECBAMF/8QAIhEBAQACAQMFAQEAAAAAAAAAAAECAzETMlEREhQhImFB/9oADAMBAAIRAxEAPwDuIAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABjqVox+dJLe0vEDID4Z5YoR21oe8n4EPLWH/v0/eRHunlPpX3g815ew39+HaV/1Fhv70fzeg908ntvh6gPFq5z4ZfWX3Rl6Hy1c8KK2Qm+qK8yt2Y+UzDLw2QGn1M9H9Gj70vJI+CvnhiHsjTj1Sfiyt3YLdLJv4ObVM5sTL6y26MfQ+aplzEv6+fU7eBHXxW6OTqNzHVxEY/OklvaXicrqZQrTXGqze+Urdlz57Fbv8RM0Xy6pSyrRlNU41YSk72ipRbdtuw+uMk9hw/LlRwhprVa3s2tG18D2N044inzShP3lJP4UXw2e6q56/bHRwAdXIAAAAAAAAAAAAAAABSrK0W+ZN9hzKpJyd27vbrOh5ZqaOHqv7El1tWXic6kZt9+5GjROaw1GYJGaewwSM7QqlrD2kwLAZYoiTJgyJMCqZEiSrYQqSJIACLgi4HmZy/7eW+HxI9LgbxGjjKkOSdF9sZxt3NnlZzS+Qtzziuy78jLwbVtDKFF9Jzi+unK3fY7a79xy2T6ruYIRJrZQAAAAAAAAAAAAAAAHi511LYaS6Tiu+/kaPNm3551Pk6ceeTfYv3NPkzHuv7atM9MWGr7DAZqhge05Oy8EOUsiIrWD0WsVZaRjuEpT1EMJhhBYBIhdwQJEIkAeJnO+JBfav3P1Pmzbrfw8TQn0a1Nvdpq/cZ85nrgvxeR5dCTWtbdp0xVyfpBEmHB1tOnCa+lGMu1JmY2sQAAAAAAAAAAAAAAADUs9p8elH2Sfa16Gr1D3886n8xFc1Nd8pfsa+zDt7q2ap+YpUMK2maZjSObqvYqlymSfMVSAiRSWwySZRskY0WZBLAIIlx5xYKqoE3CYGu5xa5x9kX3v9jzqZ9+Xn8tuivFnwLadJwrXeMzK+ngMO/uox9zifpPaNS4L6+lk9LoVKke16f6jbTZjwx5c0ABKAAAAAAAAAAAAABz7O2pfFyXNGK7r+Z5Fz0M4JaWLqv7VuxJeR57Z5+fdW/DtgyiLEFVhghEoCrZWRJVgFtEtpZIqSJSJAYQoSLEWCGs5ad679iXhc+JH05Vfy896+FHzJnSIrqPBBib0q9PozhL34tfoOhHKOCTEWxNWHSpKXuTS/WdXRq19rJsn6AAXUAAAAAAAAAAAAIkwOZZSletVfPOfxM+ZlpO7bfK2+0qzzby9CcKyRDDfsICUMRkGVuBLIIuRFgZCltZLZAFyGL+wiTJQgrJXLdaIuENQyh/Vn+J+hhRmxTvUm+eUvFmNo6IraODbEaOUaS6cZx/I5eMUdrPz/mxXVPG4efNWpp7pSUX3SZ39GjVwzbZ9pAB1cgAAAAAAAAAADDjJWpzfNGT7jMfJlaVqFV/dz+FkXgjmSROjvIuWPOeixte0rJFmylwIkyA2LgRItTRUvyARYgm5FwJK2JKkg4l0ihIVadW+c39p+JUvNa3vKWOkQtRqOMlJbYtPrTv5H6OpSvFPnSfbrPzafoLNmv8AxMHh589GnffopPvO2q8uG7/HpgA7uAAAAAAAAAAAB52cErYWr+B9+o9E8rOeVsLU3RXbJIrn21bHmOeskgls89vY5GPSuWqMhagKPaTawW0mTAhFirZNwIW0gtHaNECoZPIQyUIDIZD+a9wQ1eUSkoH0WGiXHxyidr4N8Rp5No88f4keypK3dY47OkdP4JKv8rVg/o1m+qUI+aZ11cuO6fTegAaWYAAAAAAAAAAA8XO+VsLL2ygvzJ+R7Rr+e07YZe2pHwb8imztq+HdGjXFyjbCbMDcTKJFmykpAStr3EsrFE3AWIYITAsuUXIuS2AsVZNyspEipFSXFe5+BRyMWJlxJbn4BV4y2F0jCqhDk3tLjPdc5v8AwT1lfER9lN/GjnMTc+CuvbGVI9KjLtjOHk2X139Rz2dtdXABrZAAAAAAAAAAADWc+n8jBfeX7IS9TZjU8/pcSkvtSfYl6nPb2VfV3xp5ZooiUzC3EkYrl56zE2BYSkFEnRAchW5a5W4EtaxphohsCUtpjqMsmYpkitymIjxJbmWGIdoMKtflBxFz7pQPlq07biwqjZODuto5QpLpKpH8jl+k1lSPXzSraOOw7+9ive4vmXx5imfbXdAAbGMAAAAAAAAAAA07P+XGor8b+E3E0vPrXVprmg+9/sct3ZXXT3xqyDJIZibFUikYlwBKZWTJIkBWciyijDHWzM2BE9jK31ESkUiATMcpE3Ie8kQtpGJ+aIojEvivqJQ+NIiSuXsGSh8NbDPauwjAYjQq059GpCXuyT8j7tHk/wDM9WhmJicSr6P8FdOpdfk2vu3lsZbfpXKycuyApSi0km7uyLm1iAAAAAAAAAAAPJyvkKniJKU5TTSstFxta9+VM9YEWSz0qZbPuNVnmVT5Ks1vUX6GGpmTzV+2H/Y3AHPo4eF5tzn+tInmVU5KsHvUl6mCeZ2IWyVN/wCUvOJvwI6GCetk51LNTFL6EXunHzaPmqZuYrXejLqlTfhI6cRYj4+Kevk5VDImIitdCp7rfgYa2CqrbSqLfCa8jrdhYj488p698ONTjJbU1vTMcHrO06JinhYPbCL3xTI+P/U/I/jjbCOuTyPh3toUn/xw9DBPNzCv6iHUmvAjoXynrzw5VoGLEri9Z1OeaeEf1Vt06nqVp5oYRSTdNytsUpScezl6x0MjrYuX5PydVrO1KnKe5alvk9S6zbcl8H8nZ4iporo09b65PUupM36lRjFKMUopbEkkl1IudcdMnLnltt4ebkvIVDD/ANKkk+k9c3/k9Z6QB0k9HIABIAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAP/2Q==</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcS6wkTgD_1AfGPcRk084QXvIN9R6_MF46VrfO516cG6fVNsjzTVRlFLUXA7K991pwAaCUcPp1RNEQeyrN627hyQWp3IC1XrObZMWKaDcWGaG3tlJO_VJWFw</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/shopping?q=tbn:ANd9GcSXJkHliTGnv0ETpw2Hfm_UOcPBvQStlZ978w4GcNKwDNiShs0sEnJ94HqNMI9ttLQvoqCgrLy-cDs8dAtkH1a-m6MtMvkDIjbBxRAL0b3ZuYmmui9B33_A</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/shopping?q=tbn:ANd9GcQK_l1s_KvHZ1tA4jaVDyiUkMcNqwu8zGC7XIW-YvmzWVSbnPAF00TgHK6VO2aSF7S0zD458kk1KwMKL-OPfbjIn5jN6m9Z6F3IMMsxVdrj-mVb5ZsjSB-wjEk</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn3.gstatic.com/shopping?q=tbn:ANd9GcR_3nBQFq5wZ_bFZLDZRosHCQlNhvtRmj32D-MUSstU7OLDEJ-omNtJ2HQx3JnNqqbelm5OR3aVekNutmRtwfissHwuZ95vfCq8Dd5_dpoGw9CTnmF0nWn3QQ</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/shopping?q=tbn:ANd9GcRSf-sC2qeYTBvET7oock9VPmN43tbEAf7-YKS5u5AXNyULz3NnQX5RRW3ogmwz-uXaoXvwBAUeX1rnGoD_H5MYZTUkDI2JyvlnR8fg5VrOsBy5F4D9--iRoA</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcQutx6BWqLt4CXRwxWil6ptLesrA3Vyvb21o2lhT1iuaK5R6ixYkKzhUoZc-UyCYwA3gMlFlGqcSa2kQgew-QC_cq39oUzeb4--Clcub8cWIRn2K1x-OrnXoUVH</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn3.gstatic.com/shopping?q=tbn:ANd9GcSCn1pwExARD7Oenj0pwqQdnGUCG3alhXKTx0w_N3smKDMiqNqmR1fkxOUW8Bl6482yfrY2AuLK_c9qubDNUzdusb6tKB-QOrywTuxBOu_aUlLcP9CcwN-NMvGp</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/shopping?q=tbn:ANd9GcSK00pzCFk6L_4dJuxITxf8bvjX4iE5in42bt64HzHxRqEZeJx9RadsGp6GUjp3OvwYDCRzinvHlN6CLIPg8Mn-IMJwsJu9UA</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/shopping?q=tbn:ANd9GcT6__bqd_u-DTEeFDz6uSyhDH18iK-kmjHhPIev2yMNVxci2QmO6_MSsVAMocfGEPur46GY7FtfEDUP4FY58EJUEHSv5YWV5NG1cjPVkd0UB6tAh9xkBPFNrw</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcRCPgUZ1s22F07uprynyDfhOkgGNLWytI1nWlFhyVyeMW7L8bx_nw8HcLYTECySNBYi7oj0EzNE-bMEvc7lZPdw2bP3gTfN275mXo6N7E-YOaThyo2jI_Ru</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcQ1DfHu388AZWjpvhqPrXUo5AtmEnjLEfrRoKLN8xb2daBi9uBrx1x_kmNJwdMemM9WzJ8tsKbmzTjrmvqVrz553DC1gnAtvMuASMJjYEHZ474k4pp_5B6Y8w</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcQ-OMnvPHXPQyyC_G8flKwVvBV3JhdXEzwbjgDqWsyzjuD7tHnHBjIxTLBop7hAi9DSdBss5rUwGvcq3316o1Vb3BcO0xINhw</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/shopping?q=tbn:ANd9GcSX8iA6hMydc8xyE03mar0qyP-7louvUKQID2gv5exQADPgSNMoHvTUV0Ydbbuq7aUhxfQR40uo_OOmd5wG6dEjUV5xuRy2It4ATgItJN0bRH_x1jFsyq19jE688XZOydKuQgUPLZM0&amp;usqp=CAc</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/shopping?q=tbn:ANd9GcTOdOhp60OIhk9t3D3KjuiWGGcQTMQQ8R-fPPBQvgeKUWrOjlAzs23OiPY9lktWi3ygO0knFakFgwj-zQ45KJz94UloLGGErbG7adke-_tpGzod9-NxQTii</t>
+  </si>
+  <si>
+    <t>https://drogueriasfarmavida.com/wp-content/uploads/2025/10/32584-1.jpg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn1.gstatic.com/shopping?q=tbn:ANd9GcST9sEGY_IL-a5Pk3F0yhJMWZGxLGQCmN6NjrEtqEIIWs8wevUXYZSda9h0UARKkJMr7pZgzLHtEFYUHVp8Pri6I1BI4K1xLU09AG0cW3hewRg9hUquAOFjHg</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn2.gstatic.com/shopping?q=tbn:ANd9GcTDG7Z4f_iGKi3ceUqsxMjzVD5n0J8fa3KKzhuSz2wSD6rCv8W7-ZFCQQ-lMrX8uSN0G3a6OhTXofroqSctM7CPQdIGHVFlj7t4jaUYBRpdPVqdeU8f_Xhc7w</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn3.gstatic.com/shopping?q=tbn:ANd9GcTiM38yr4gyqWdQWlI-pCSqSee9UdeXfNq_Q55Nc0xgiTMjrGLziMLzS2hXC6NtROfZg9WIV1uEffJ_CC7TBRG7UjDmVPOzKHNKPd6daoaE_HXNqpZZ6PTg8Q</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRkgGAABXRUJQVlA4IDwGAADwIwCdASqVAAoBPj0ejUUiIaERKgScIAPEtLd5O2vp8y/0zrnHCvn55MkGHrR8kPnOQQcJ/Ivup+R/Ln5Vds/9Hl3mUv8P4YOoj3Y9CH8388vDb+t+oB/OP7r/xfuO+Uv/Y83P1N/z/cJ/Vn/jfrj3DvQ6/aUUCgA6CFUQBXdRJjuADoEd6ajeJoYAdBAYiHNpe22G6qHwvwtC3aevNahpRm2nkOCItBQbADoIFmdDH4JOghUqSNAi1+qAk6CFWuSnC9wio8m8wFpVGf4/pQHTDxIzLxjz0D6ay16GHbCd+LmgJnLnbUSWDdaO5EU7yCcuSlkudpHT/vR2GlBywJMtH2qXwNwVUm2DR9qlcatpnsxkOF9Mks8mUSH7YUAHMcfBl421FKnwAAD+/zoIOMiqxnXYl5Lhlx2SkEBIUZaHnYs+w2wuP2fyDEtkqVEmjNLG/2lYtgjkUm4CTBecX/KcUDnRGl1ILJH6+WkjYIYxHp1oyDnk1B1oOYYQ59023fiiH6ByBp3t+6B3v0glaWv+vzNPFYN/THdiulwbKLZFs+qtIXgij/E4KH1VLH/+RLs8TbsFasK67PSeb/JhJJhjEDk3ueY/+Oim0uJWL4XvhJbJXi5fupkGCD9ToeYHopMBSPPYnA09WdD5pGr1/vT+aj7l1lnlKPWQMw0ijsayxkGFZqguKMfSi0mU83EYmxdhCAKREaQPMDFxOqNgcbPn4FunZwhmRlYWaGqoP20n3dFq+kZcXH8qv3NscZBUIuQ4mNOP48+v6207MxfVsKXhheAh6fSfgUm51zO2EdlrFka6AERPga/yCeF+yYMWXxCeAHi5MnbusJxoFsaF0GQapwuyLLZ+3U01wFLD57ckAompds5OoIs/5tGon8lm+N5oeCj2PzTKHfvlnjjfeUdi/qWAd//39nesd4gV1EuVqqFVb6/kG7K/CH4E8Q7inH5qJBi4STYEvAugU4wkjtX8aRbZrX3ah42eHPrR/F4fnqVC/cRDIiRxqXr5NhtiAta5+wSnVcnqbviui89EMD3uViOLzBpPb/i4V8KDEFXI9uQI5Bau9A8lDviWdfiybZd+nmpPlvxkhIX1d+ps0jeN+PbjQKVds3/8mqfTTK7/ei2xHI3O/LdSLGR15taDnSoUV0D0wGVyDB7ru11QGUzOpgAVZgaZW8zn0GZTxInMH7SBvPapKtBaHRavEz7Y/vsulknG2DR1cyO7EPZFd2H90WbPD8lZWwR1LNuJHuN9mDyJ+8MciC0mhvF8idzfSDX7KkPGD+aC4kjneXJH+cXhQuT/0Nkb9c6KXRFpqKU2eO5vQHlS6ce2FnhBc642787n3/Qu/4UZqUIjj6/5ZxJx+7OvTzgIFD5m+G2XT/+HLxe4oK6N1FMFm377ea0dUe8HTxtXxbYrN61FhngOMb0cYdhb/Moc88i221BrGbNGed3QxOSgLz2/lez3XUId0z07+Ipsk0LDef/OKATceA3n3jUwEixN9Gfb4lpq3hJlnBP/c+Fe1Apgoux9uqeBA4PCuwAXiAKu52rO+z5ujkz181NKp0v8apZ+HXagReNMbNvCqJXorLr+Ngbwybd5tVvjBOB8Ww6eRK0iySv4cnWLoF4/wsxJwATS/z1UudPl74NJ5bbay5eLFubLQ8DVTpcDK8zc13dQlLNAahS9U11kUhBnJWhUFAzXls75x0AohkFzIW2SEmp1b7b+QS6NQX79Hn8oeKwUQYxozx47ms7P0dscpA66dKQZk/3DfZHBrwOyXlI5I/IKkQ1JV4/vaPjHVZEaPjp+iTt/K+cjsmoUgqH3VtBKFH9jSdRHgrpVYOPre8ItdqXpY84BlhkhGIl6HmEz5wdKZEQdfTBu3i/9kSEIfCZfi/5y3omKeZyOkekZQ76va9TdOM6KH1QfJmbxRzm8jjPb0OOwKDpNH3pYK3XKlscfPp7G+BkWY8KE1zJ004yE8Q4towhgnVCkSLOHN2SBC/Xh5QLWJ/wEriCIgXqcVuvbkb71iz33adMK/kwHfTWViRHZm4Zfjtvs02n5eGkcg0Ti0ghZbI6mr7/rbnSSyofX4cgnaS/dF3wZ4tkvdEQ64Xj/sbTDgXwVmezedyGJLpJD4AAAAAA=</t>
+  </si>
+  <si>
+    <t>https://images.rappi.com/products/246246909081_vnqrzobvefso_816580274028_fratuakgrduxit_6921875009193_1.jpg</t>
+  </si>
+  <si>
+    <t>https://surticosmeticosb2c.vtexassets.com/arquivos/ids/170823-800-auto?v=638503690121470000&amp;width=800&amp;height=auto&amp;aspect=true</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBxAQEBUQEhIQFRUXEhYSFhUWFRcXGBYVFRYWFxUWFRYYHSggGBolHRUXITEhJSkrLi4uFx8zODMtNygtLisBCgoKDg0OGhAQGy0iICUtLSstKystKy0tLS0tLTctLS0tLS0tNS0rLS0rLSstLS0tLS0tLS0tLS0tLS0tLS0vLf/AABEIAOEA4QMBIgACEQEDEQH/xAAcAAEAAQUBAQAAAAAAAAAAAAAABQEDBAYHAgj/xABCEAACAQIDAgoHBQcEAwEAAAABAgADEQQSIQUxBgcTIjJBUWFxsRQjUoGRocEzcnOy0SQ0QmKCkvCiwtLhY5OzdP/EABkBAQEBAQEBAAAAAAAAAAAAAAABAgQDBf/EACgRAQACAgEEAQMEAwAAAAAAAAABAgMREgQhMVFBEzOBYXGR8CIjMv/aAAwDAQACEQMRAD8A7jERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQEREBERAREQKMwG8gTyay+0vxExNqDNlW2pJN/Aa+cwauBNublJv/ESBbr3KYExy6e0vxEp6Qntr8RI30Fe0x6Enf8AGBJek0/bT+4R6TT9tP7hI70JO/4x6GnZ8zJsSHpVP20/uEel0/bT4iYHoiez8zHolP2fnG0Z3plP20+Ij0yl7afETA9Ep+z8zKehp7PzMbVn+nUvbX4y9TqKwupBHaJD1MEpGmh79frL+EprTN9fcfpGxJxKAysoREQEREBERAREQEREBERAREQEREDBx556f1fSVnnH/aJ7/pPUShERIEpKxApERApERIKShlTKQJGIiaUiYG0dpCkcoUs1r2vbTxkXU2/W6qajxzH9IGxxNRqcIsUNyUvg3/KeqPCasRqif2t/yhNtsia4nCGp1op8Lj9Zn4LbK1GCsjIToOsX7IVKREQEREBERAREQEREDAx/2ie+Y208eKCBsjuWdaYVctyzmw6RA+cycf8AaJLG0cCldAjFxZ1cFTYhlN1IPjLGtxsjW+6NqcJqQUtkq3FOu7KQoZTh7coh1tm5wtbTvgcJqBYhOeA2HUshVhfEOUUXB3qRrLzcHsOVyWe2SshOckty9uVZidSxtvlyrsSizZiGv6ncbfu7F6fzOvbN/wCtv/BhDhQlmZqVVQFrshOUip6OSKgWxuDp1gStDhItQAJRqNUZ2QIGTXIquzcpmy5QHUb95tPb8H8NTSoxFVgada4Lscq1btV5ME2UnXWRGExGCq005OniU/aAtPK6hketTLnIyOQqkDVb6E6iaiKT4hrVZ8Ql6HCAVSi0qNR2ZSzrdV5IK5ptmJNi2YEWF72M80+EKkqeSqCm7VEp1brZ2phiRlvdQcjWJ32kR6XhFpJWGHxdLknegoVwHbIXesGKVDnUGmzNc6nde8vNUwlPFGktGu7XbIBUBph61Jqh5Omz8wsuYZrWBY6i5jhX1/f5OMemQeFqikaj0XQ8nSrKpZLNTrOEVswNhYnW8rX4TqmZjTdgEwzWQq1/SDU1UjpEBPfpaQvpOCp4cE4bFBagNiawNTJhWUjIxqXADNoikG4OklmfDCu6ClWqVEWmwY1D6xsMFcLmdumorgm++532lmlY+FmtfS/X4T0xTaoiNUtV5NQpHrAKIrF17gl/h3ycpOGAYG4IBB7QdQZptI4R0V1wDvmR8YaZZCqpUt6zKzZczZNFGosd02rZIpcjS5G/JcmnJ7zzCBl367rTzyViI7MXrEeE1ERMMIHap9cfugef6zykrtX7Y+A8p5ErMr4A7IyjsECUBkFGAlgdNPvr5iX2MsrrUQfzr5wNiiIhoEREBERAREQERECPx/2i+H1M9y3j/tF8B5mXIlCIiQeatMMpU7iCp8CLGa7snZuH5TIFxAam1KqDUIuRTFSnS0G5bZtCAToZssjqeywrMy1at3dXe5Bvb+EWAsLADwli0x4WJmEOcLhHzgUq9UU6lRgLjKzYlmao4NxzbqwuSBbtvL2DwmCpCliszoSi5GducUWkFyt2jKASO1QZnNsGhZ1VSgcKrBDluq303aA317ZkV9nU3VVbMQqsgN9bOpRrntsZedva8p9oetg9nGmgZxlpmoqHObqxK1WYEagiykN1XHbLjbPwdOpyhBDZi5q3N2auHGU26VxfTq5vdL+P2Erg5GyFs4ZucTZ6a0yBZhpZF0NxpM0YBLAG5s4qXvrmAsu7qAsPdHO3s5T7QdbD4F1oohqEDk8KOTqOhNJ1LKtQggulkPz75slKmFCqoAAsABuAGgAke2wqBULZxlyWIdgRyasqWIN9A7fGSNMWsPAdsk2mfKTMz5SEREDXtpG9Zu6w+QlaaSzwzxK4Og+LtcggFCbZr6aG2htr7pouF428JuehiV8MjD8wPylZl0ULK5Jo442NlDpPXXxpMfy3mRheM/ZdUlUqVSQpcjkXHNUXJ1EGm2usx0a1VPvr5zSMVxwbM1yLin8KYHzZhNo4D7VpbVpHFIHRVq5MrZc11ANzYkAayGm6REQ0REQEREBERAREQIvalUI2Y7lTMfAXJ8pqeI4yMGvQp1377Ko+Zv8AKbNwg6L/AILeTTgaGdXT4a5N8nR0+Kt97dRXjLw/XQrjwKH6iS2z+G+ArG3K8meyoMv+ro/OcavF50T0mOfDonpaT4fQyMCAQQQdQQbg+BlZw3YfCHE4Nr0n5t7mm2qHt5vUe8WM6zwa4R0cdTunNdenTJ1XvHtL3+U48vT2x9/MOXLgtTv8JmUlZSeDwJQyspAQm8eI84hN48R5yDPiJpvGNwmGFomijWqOpufZTrPiZpWg8bnCwV25Cm3q00+83W3h1D39s5NUq21mdtPFGo5MisQdQIFa9csLELa99AL7va3+68vYLaJo1TVppSFwVyspdQG3gByb+8mYvXKEQaemOvV7hadD4nuFnoWK5Fz6qrYN2A9Te79Zzq8u0nKkEbwbiRX2cDfUSs59xScLRjMMKFQ+spiwvvZR1eI8p0GVCIiAiIgIiICIiBD7dGjfhHyacAWfQG2ev8M/7pzXi/4NYbG0qjVg5KuqjK2XQrednTXilbTP6Orp7xStpn9GlxN04f8ABvDYKnSaiHBd2VszFtAARNY2Hh0q4qjSe5V6yI1jbmswBserfO2uSLV5Q7K5ItXlDCmRs3HVcNVWtSazKdOwjrVh1gzq1fgFs8KxFOpcKSPWP1DxnIAZimWuXemKZK5N6d52HtVMXQSummYar1qw6SnwPytM+cv4rNqFK74Ynm1FLr+Im+3it/7ROoT5ubHwvp8/LThbRKSspPJ5kqm8eI85SVp9IeMgrtnaK4ag9ZtyjQdpOgHxnzjwz24+IrM7G5JufoB3TsHG7iGXCIB1uSfcunnPnzFsSTNKxybzEqnnHxmYqzHq4Zhc2033+cKsieZ7VTKvRZbXBFxcXG8do7ZFUy6X790LCG0oNJUT/BDblTB4lKqG1mH+GfUuxNqJi6CV03MNR2HrE+PwJ9B8ROLZ8FUViTlcW+BB/KIR0yIiAiIgIiICIiBE7X6R+5+s0viiPqK/4iflM3Xag539P6zSOKL7Kv8AfT8pntX7Vvw9afbt+ErxgbDr4ynSWiqkq7MbsF0K265qOzuCGMwtaniqyoKdF1rVCHDEJTIdyANSbA6TpG2tt0MGqvXYqGbKLKW1Av1CQOP4X4LFUqmFpO5qVqb0KYNNwC9VSiAkjQXYazeLJkiuojs3jvkiuojsvvw5wDjItRyzDIBybi5bQC9u0zSRxebQ7KP/ALP+pcw/ALHU3Wowo2Vlc+svopBNhbsE248Yez9+at/6z+s39v7Pf38t/wDH2u/v5aDs3CVcDtOjTqWzrWpg5TcWqWG/wadonH8dj0xm16dWlmytWoAZhY83IDp7jOwTHU7njM+dMdRueMz50SkrKTlcxK0ukPGUlaXSHj9DINP44B+yp95vyzj+N4HY9aa1hh3dGQODT55AYXF0XnA2PZOw8b/7on3m/LMjAYg0sBTqAAlcNTaxNhpTXebGw75tXzrWpNTNnVlPYwKn4GeWq7rqGAOqkkA9ViVIPwM+iU4Q4eplWrTvmygaB1JbkRoSN164sTvAJ7BMGrR2JWGZ8JQ6KNrhtTygpFQuVec3r6dwNedHGV1L58wu0qtFs1MhD1EAEjwveVx21K9c5qtR6h7WNzp9NTO9Dg1wde/qML0OUJuyqFyCp0r2vkIa17gG9rQnBLg9dQMPQuwuATU3c61wTpfI1gd+U2jUn4clw20+S2eFFHCkuHuxw6GpbNYHlTr8prBfO2pA7v0E+im2ZsNKQthsOyhKjqppM1lpqHe4YHKLMp135ha8vJtPZuHDclRopkqck2SmlMhg5Rt9tBlZu8Lpc6Sak1PpwfZnBbHYkgUcNWYac8rkTxzvZfgTO/cVGwHwOGanUZS5IZsvRB52gJ3+Mz8c7XIzWG7qvu7TM3gqLK/iPr26yJtOxEShERAREQERECL2j0/6R5maNxRdDED+an5PN7x49YPAec4DQxVWnfJUqJfflZlvbdex1nVgpzrav7OjBTnW1f2dK42x+z0fxj+QzQODX77hv/00f/osxMRjKtSwepUcA3GZ2ax7RcyyrEEEEgg3BGhBHWD1GdmLHwpxdmPHxpxfQ2KHq2+43kZ87ruHhMhtoVjvq1f72/WY4BJsAT1ADt7AJjDh+nvuzhxfT33bXxa4A1ccKlubSU1D94gqg+JJ/pnX5r3AfYXoeGAcetqWep3G3NT3D5kzYZw9Rk537OLPflfsSkrKTxeJPVHpDx+hnmeqPTHv8jA1HjeA9EXtzN+U/wDU5VsrhRjcKRydZyoA5jkulgN1juHgROp8cJ/Y0++fyzkNbZNdaCYop6pzlDgjpAkWI3g80z2xa+Xrj1vu61wW4T4baHNZESuACUYA5rFWzU2/iAKqbbxlHYDMrbmycJSw9SocOjAIgKFmClVNIAWvZRanTvYahADOKYaqyMHRirKQysDYgjcRO28DeEAx2HzGwqoQlUDttowHYw18bjqmr04948LenHvHhActh6gp5qHq3IRg2JYLTL4Ni9VRk1YUkdc1xfQ9ZM90Np0qz0VyVXeqWV1evYcpTsaRqZads2WqrdVhbRiAJuDpUzNuINgtyCBobki3utrPNKnV1JtfIN9jztLnQX6v80nnzY5NRw+IpPSp/sxJbC5l9dVqX5daaBGIUFxlFO4GoCmw0vMlRXc8omGprmIsTQ5yl05Rkql26JevWBYAWswHSm0eu0F1trci2mn6zy2Ga4Jc6NcC3V1D4dck2SbMPGdM/wDXYOzXyknwY6L+I8jIzFgknda9u34gafEyU4M9B/vDymGYTUREqkREBERAREQInaDeuA7h5zgDjU+J853vaR9ePBfMzmOM4vseGJUUnBJIyuBvPY1p19LetZncunpb1rM7lqETZqfAPaJP2KjvNRPoTJfZ/FpWY3r1qaDrCAufibAfOdc58cfLrnNSPloaUyxCqCSTYAC5J7ABvM6fwH4F8gRicSBym9Ke/k/5m7X7urx3bHsLg1hcGL0ku9rGo/Oc+/co7gBJecebqeUar4cmXqOXapKSspORykpKxApPdHpD3+Rnie6HSHv8oGnccP7mn4tv9DfpNawuyKuL2HRpUQpYVC9ibXAepcA9us2LjlP7HT/G/wBjTWMJtx8Nsai9CogqLWysOaxAZqhsyndcWM9Kb+G6732ZmOFMbI9DbkziqaIGogq1VTyisbBbk803uOqQnFxjGo49aZuBVVqbA6agF0Nu26kf1GTdCiKVNdvMWaqVVnpCyoS4FHmGxK6EHW8xxwhXaO0sCUpuhR2zZiDfQNoR3IZ6x4mHrHiYdMgRKic7mDPDT2Z4aQReKGp8f836fAGSnBo3V/vDykXiN57e7/L+Uk+DO5x/MPr+kLCaiIlUiIgIiICIiBCbU+2HgPOZwmFtT7X3CZoiUIlYkFIlZSAiBKZh2jfb39kCspKy1Rro9yjK1jY5SDY9htA9z3Q6Q98tVKgW1za5yjvJubfIy7Q6Y8DA03jk/c6f43+xpxcjd4TtPHH+4p+MPyPNUPF8K9GlVoVQhalTZkcEjMVBJVhqPCxntitET3emO0RPdqg27ijhzhDUJo2AyEKbAMGFja41HbNz4q9iNmbGuLKAadK/WT03HcLZfe0v7F4tURg2Jq8oBryaAqp+8x1I8LTf6NNUUKoCqAFAAsABoAB1CavkjWqt3yRrVVwSsx1xia66g5bdc9NikHXfw9/6GeDwXTLbmYFTLYHMWtl7RffYknw+InpFBcELU3kkt1dIW+Mgs4g7/E/4bafEyU4NrZXPePr+sia7/wCe/wDzd8ZM8Gx6on+c+QghLRESqREQEREBERAhtpj1nuEzFmJtMes9wmWu6JRWIiQWMdRz0nQfxKV6WXf/ADAG3wMjaWAxICrnphQhUqLAa57jKFAN7rqLWynTWTMQIhcBiQuQVQAEstid+WmLbtBzH1GvP7pbxeDdAajVwihw51bm82moN97EZW6Whz67pNyzjMOKtNqZJAZSpI32PZAiSqLytOpiG51JlYXc5dWJKk3AIWogyjXQds84bBIQKrVksci81TSUrSzjKwLXvdje/s2tM/FbMWo7Oz1NUyBRlsuoN1utwbgHfrYX3TzV2TSamKbFiByhvcXJqhg5Olr89jpAwsJgaYqgctna/Kiw0Ips6nM1yC16wv8AdEnsP0x4H6SPp7MprUFRc4ILbmsDnIYgjrFwNO6SGH6f9J8xA1HjhW+AXurA/wClx9Zr/BPh5g+Rp0K78i6IqXfoNlFrhxou7+K06Dws2V6VhXp2uekB2kA6eOvxtPm3bez2pOV7DKrvxrVHblKDLUplNMrIy311394+E9jHVgNaeoGtwbfwDfu3l+vqHjPmvD4mrSOam70z2ozKfipEncJw52pT0XGVv68tT84MGneVxw38mu4G38WoUkgW3a7+0S7TrqVvyVtWWxAGi5v0+c4thuMzag31qbeNKn9AIrcZ21OqpSHhST63iEmJ+HazijbRP88PpKGqy86oVVRe5NlA363J8JwXF8PtqONcXUH3Vpp81UGa/isbWrterVq1De/rHZ/hmOk1No+IZik/Muzbb4bYOldKbriKnZTvyY+/U3MO4Xm98DKrvgqbv0mux95M+fOCex2r1lWxNyNB190+ldm4QUaSUh/CoHv6/nMtsmIiAiIgIiICIiBhbTpXXN2eRhN0y3UEEHrFpiik40yj+7/qERfCCpVVE5PlPtQGyBicmVr3ygkC9twkT6TjilMhK5KBqj6Acp6w5UN7EjIDoBfVdJtfJ1Oxf7j/AMZXkn7E/uP6SDWDUxTHIBiAQ9dy1tCjK3IhcxAYgkWXqtLVGnislmXEFOUQvZmV2XK2bKGbMOdlvZteqbbyLfy/E/pKig3aPheBqvouLIOXlVHo9QZaj52N3JVQwIyvltZje3aZMYWjWCIGYFhvOXcMtgCM2p75J8ge35f9yvId8sTpJrtFpTqi2/6W6wde2/UeqeTh3YWN93WevK4PWe0SW5Adp+UejjtM9PqS8/oR7lGrQN76g5lPSJ0AAIPb1zMw3T/pPmJf5Be+VSkAbjwmJmZ8vStIr4XJznjE4AviicRhQC51emSBmPahOl+4zo0SNPknaeCq0HNOrTdGG9XUqfgZgkT67x2z6NdclalTqL2OoYfMTVcfxXbIrG/o5pn/AMbsvyvb5QPm4EyhJM75U4l9mndUxa92dD5pFPiX2aDrVxjd2dB5JA4IFknsXZlbEVBTo03qMepRf3nsHeZ3/AcV+yaJv6Oah/8AI7N8r2+U2rBYKlQXJSp06a+yihR8BA1Pi94GHApylbKaxG4ahB1i/W3fN0iICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgIiICIiAiIgf/Z</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQI2LeIB3dg2xGT6VUNmWHuBGxcflUXYSCrfA&amp;s</t>
+  </si>
+  <si>
+    <t>https://www.farmaexpress.com/dove-women-dermoaclarant-sobre-8-5-g-10uds-200039617/p?srsltid=AfmBOoofR_3gusqlUlFEOm-y064ggNDsch2Fr2QMHzbWzEi7UoF19gc7</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSWBNC42rv-CSeOPz1HJUceY6kMzGRBJFUJFA&amp;s</t>
+  </si>
+  <si>
+    <t>https://surticosmeticosb2c.vtexassets.com/arquivos/ids/171484-800-auto?v=638528612663400000&amp;width=800&amp;height=auto&amp;aspect=true</t>
+  </si>
+  <si>
+    <t>https://www.surticosmeticos.com/encrespador-bon-shik-bs-42/p?srsltid=AfmBOop9odI8xE4C7_ISLxf8LbeozKEmxH2VZWDz9bmNmVJxmOfAYV4W</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSLylduA7DRafcMeXZXwtn-eaRr6qJPi1UxJw&amp;s</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcSRicKSivKCevPRhLqO2P2KySo0XyJJwi3XCA&amp;s</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTn5Z0dCdt6B174XFxfqbBpL6bhgMscFo6TBg&amp;s</t>
   </si>
 </sst>
 </file>
@@ -303,8 +408,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7450E731-C284-474F-B115-531F72DAE462}" name="imagen" displayName="imagen" ref="A1:C64" totalsRowShown="0">
-  <autoFilter ref="A1:C64" xr:uid="{7450E731-C284-474F-B115-531F72DAE462}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7450E731-C284-474F-B115-531F72DAE462}" name="imagen" displayName="imagen" ref="A1:C405" totalsRowShown="0">
+  <autoFilter ref="A1:C405" xr:uid="{7450E731-C284-474F-B115-531F72DAE462}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EB4D1AAA-C9B5-41CB-92F4-C4AA5A191094}" name="id_imagen"/>
     <tableColumn id="2" xr3:uid="{D57247A9-017A-439A-98A4-6FB2011C2D61}" name="Código"/>
@@ -577,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C405"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -1288,16 +1393,3167 @@
         <v>63</v>
       </c>
     </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>55481</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>55743</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>55188</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>53701</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>55797</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>55796</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>55635</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>55636</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>54097</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>56113</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>55825</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>54827</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>55570</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>55846</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>55996</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>53559</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>55320</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>55302</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>55311</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>55301</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>54231</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>55941</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>53042</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>55026</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>55738</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>54703</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>55739</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>56152</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>56100</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>55149</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>55118</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>54269</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>55255</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>53703</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>56188</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>54129</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>55430</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>55579</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>55373</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>54604</v>
+      </c>
+      <c r="C104" s="1"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>54525</v>
+      </c>
+      <c r="C105" s="1"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>55120</v>
+      </c>
+      <c r="C106" s="1"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>55760</v>
+      </c>
+      <c r="C107" s="1"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>55267</v>
+      </c>
+      <c r="C108" s="1"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>54632</v>
+      </c>
+      <c r="C109" s="1"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>54350</v>
+      </c>
+      <c r="C110" s="1"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>54008</v>
+      </c>
+      <c r="C111" s="1"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>54012</v>
+      </c>
+      <c r="C112" s="1"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>54523</v>
+      </c>
+      <c r="C113" s="1"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>55268</v>
+      </c>
+      <c r="C114" s="1"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>54526</v>
+      </c>
+      <c r="C115" s="1"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>54522</v>
+      </c>
+      <c r="C116" s="1"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>53958</v>
+      </c>
+      <c r="C117" s="1"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>54355</v>
+      </c>
+      <c r="C118" s="1"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>56166</v>
+      </c>
+      <c r="C119" s="1"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>55821</v>
+      </c>
+      <c r="C120" s="1"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>55745</v>
+      </c>
+      <c r="C121" s="1"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>55004</v>
+      </c>
+      <c r="C122" s="1"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>54028</v>
+      </c>
+      <c r="C123" s="1"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>54705</v>
+      </c>
+      <c r="C124" s="1"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>55229</v>
+      </c>
+      <c r="C125" s="1"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>56009</v>
+      </c>
+      <c r="C126" s="1"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>55648</v>
+      </c>
+      <c r="C127" s="1"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>54564</v>
+      </c>
+      <c r="C128" s="1"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>56128</v>
+      </c>
+      <c r="C129" s="1"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>55502</v>
+      </c>
+      <c r="C130" s="1"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>55511</v>
+      </c>
+      <c r="C131" s="1"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>53938</v>
+      </c>
+      <c r="C132" s="1"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>56065</v>
+      </c>
+      <c r="C133" s="1"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>55705</v>
+      </c>
+      <c r="C134" s="1"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>54840</v>
+      </c>
+      <c r="C135" s="1"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>55672</v>
+      </c>
+      <c r="C136" s="1"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>55591</v>
+      </c>
+      <c r="C137" s="1"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>55976</v>
+      </c>
+      <c r="C138" s="1"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>56072</v>
+      </c>
+      <c r="C139" s="1"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>56182</v>
+      </c>
+      <c r="C140" s="1"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>56183</v>
+      </c>
+      <c r="C141" s="1"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>54892</v>
+      </c>
+      <c r="C142" s="1"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>54591</v>
+      </c>
+      <c r="C143" s="1"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>56051</v>
+      </c>
+      <c r="C144" s="1"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>55611</v>
+      </c>
+      <c r="C145" s="1"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>55513</v>
+      </c>
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>55514</v>
+      </c>
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>54501</v>
+      </c>
+      <c r="C148" s="1"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>54602</v>
+      </c>
+      <c r="C149" s="1"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>54601</v>
+      </c>
+      <c r="C150" s="1"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>56083</v>
+      </c>
+      <c r="C151" s="1"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>56010</v>
+      </c>
+      <c r="C152" s="1"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>54933</v>
+      </c>
+      <c r="C153" s="1"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>56035</v>
+      </c>
+      <c r="C154" s="1"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>55896</v>
+      </c>
+      <c r="C155" s="1"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>55872</v>
+      </c>
+      <c r="C156" s="1"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>54884</v>
+      </c>
+      <c r="C157" s="1"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>56086</v>
+      </c>
+      <c r="C158" s="1"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>55607</v>
+      </c>
+      <c r="C159" s="1"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>55604</v>
+      </c>
+      <c r="C160" s="1"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>55605</v>
+      </c>
+      <c r="C161" s="1"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>55606</v>
+      </c>
+      <c r="C162" s="1"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>54796</v>
+      </c>
+      <c r="C163" s="1"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>56191</v>
+      </c>
+      <c r="C164" s="1"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>56190</v>
+      </c>
+      <c r="C165" s="1"/>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>56189</v>
+      </c>
+      <c r="C166" s="1"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>56004</v>
+      </c>
+      <c r="C167" s="1"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>56112</v>
+      </c>
+      <c r="C168" s="1"/>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>55957</v>
+      </c>
+      <c r="C169" s="1"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>55087</v>
+      </c>
+      <c r="C170" s="1"/>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>55464</v>
+      </c>
+      <c r="C171" s="1"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>55958</v>
+      </c>
+      <c r="C172" s="1"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>54281</v>
+      </c>
+      <c r="C173" s="1"/>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>55815</v>
+      </c>
+      <c r="C174" s="1"/>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>55813</v>
+      </c>
+      <c r="C175" s="1"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>55814</v>
+      </c>
+      <c r="C176" s="1"/>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>53135</v>
+      </c>
+      <c r="C177" s="1"/>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>55155</v>
+      </c>
+      <c r="C178" s="1"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>54939</v>
+      </c>
+      <c r="C179" s="1"/>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>55725</v>
+      </c>
+      <c r="C180" s="1"/>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>53136</v>
+      </c>
+      <c r="C181" s="1"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>55476</v>
+      </c>
+      <c r="C182" s="1"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>54346</v>
+      </c>
+      <c r="C183" s="1"/>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>54098</v>
+      </c>
+      <c r="C184" s="1"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>55080</v>
+      </c>
+      <c r="C185" s="1"/>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>54789</v>
+      </c>
+      <c r="C186" s="1"/>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>53108</v>
+      </c>
+      <c r="C187" s="1"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>54273</v>
+      </c>
+      <c r="C188" s="1"/>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>54498</v>
+      </c>
+      <c r="C189" s="1"/>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>55979</v>
+      </c>
+      <c r="C190" s="1"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>55763</v>
+      </c>
+      <c r="C191" s="1"/>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>55762</v>
+      </c>
+      <c r="C192" s="1"/>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>54338</v>
+      </c>
+      <c r="C193" s="1"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>54337</v>
+      </c>
+      <c r="C194" s="1"/>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>54341</v>
+      </c>
+      <c r="C195" s="1"/>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>54233</v>
+      </c>
+      <c r="C196" s="1"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>54270</v>
+      </c>
+      <c r="C197" s="1"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>56177</v>
+      </c>
+      <c r="C198" s="1"/>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>55385</v>
+      </c>
+      <c r="C199" s="1"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>54691</v>
+      </c>
+      <c r="C200" s="1"/>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>55132</v>
+      </c>
+      <c r="C201" s="1"/>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>55506</v>
+      </c>
+      <c r="C202" s="1"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>55166</v>
+      </c>
+      <c r="C203" s="1"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>56194</v>
+      </c>
+      <c r="C204" s="1"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>54190</v>
+      </c>
+      <c r="C205" s="1"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>54893</v>
+      </c>
+      <c r="C206" s="1"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>54931</v>
+      </c>
+      <c r="C207" s="1"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>54799</v>
+      </c>
+      <c r="C208" s="1"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>55528</v>
+      </c>
+      <c r="C209" s="1"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>53778</v>
+      </c>
+      <c r="C210" s="1"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>55770</v>
+      </c>
+      <c r="C211" s="1"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>55081</v>
+      </c>
+      <c r="C212" s="1"/>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>56068</v>
+      </c>
+      <c r="C213" s="1"/>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>55776</v>
+      </c>
+      <c r="C214" s="1"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>56075</v>
+      </c>
+      <c r="C215" s="1"/>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>55490</v>
+      </c>
+      <c r="C216" s="1"/>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>54423</v>
+      </c>
+      <c r="C217" s="1"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>55661</v>
+      </c>
+      <c r="C218" s="1"/>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>55261</v>
+      </c>
+      <c r="C219" s="1"/>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>53956</v>
+      </c>
+      <c r="C220" s="1"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>55527</v>
+      </c>
+      <c r="C221" s="1"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>56002</v>
+      </c>
+      <c r="C222" s="1"/>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>54489</v>
+      </c>
+      <c r="C223" s="1"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>55836</v>
+      </c>
+      <c r="C224" s="1"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>56127</v>
+      </c>
+      <c r="C225" s="1"/>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>55305</v>
+      </c>
+      <c r="C226" s="1"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>54977</v>
+      </c>
+      <c r="C227" s="1"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>54042</v>
+      </c>
+      <c r="C228" s="1"/>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>54043</v>
+      </c>
+      <c r="C229" s="1"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>53953</v>
+      </c>
+      <c r="C230" s="1"/>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>54077</v>
+      </c>
+      <c r="C231" s="1"/>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>54076</v>
+      </c>
+      <c r="C232" s="1"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>54998</v>
+      </c>
+      <c r="C233" s="1"/>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>55773</v>
+      </c>
+      <c r="C234" s="1"/>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>55282</v>
+      </c>
+      <c r="C235" s="1"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>55280</v>
+      </c>
+      <c r="C236" s="1"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>55105</v>
+      </c>
+      <c r="C237" s="1"/>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>53562</v>
+      </c>
+      <c r="C238" s="1"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>54480</v>
+      </c>
+      <c r="C239" s="1"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>55440</v>
+      </c>
+      <c r="C240" s="1"/>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>55216</v>
+      </c>
+      <c r="C241" s="1"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>55215</v>
+      </c>
+      <c r="C242" s="1"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>53952</v>
+      </c>
+      <c r="C243" s="1"/>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>55853</v>
+      </c>
+      <c r="C244" s="1"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>55402</v>
+      </c>
+      <c r="C245" s="1"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>54406</v>
+      </c>
+      <c r="C246" s="1"/>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>53752</v>
+      </c>
+      <c r="C247" s="1"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>55600</v>
+      </c>
+      <c r="C248" s="1"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>54121</v>
+      </c>
+      <c r="C249" s="1"/>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>54308</v>
+      </c>
+      <c r="C250" s="1"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>54318</v>
+      </c>
+      <c r="C251" s="1"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>56160</v>
+      </c>
+      <c r="C252" s="1"/>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>56198</v>
+      </c>
+      <c r="C253" s="1"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>55337</v>
+      </c>
+      <c r="C254" s="1"/>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>55290</v>
+      </c>
+      <c r="C255" s="1"/>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>56202</v>
+      </c>
+      <c r="C256" s="1"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>55182</v>
+      </c>
+      <c r="C257" s="1"/>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>55706</v>
+      </c>
+      <c r="C258" s="1"/>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>55189</v>
+      </c>
+      <c r="C259" s="1"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>55363</v>
+      </c>
+      <c r="C260" s="1"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>56081</v>
+      </c>
+      <c r="C261" s="1"/>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>53230</v>
+      </c>
+      <c r="C262" s="1"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>54259</v>
+      </c>
+      <c r="C263" s="1"/>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>56148</v>
+      </c>
+      <c r="C264" s="1"/>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>55109</v>
+      </c>
+      <c r="C265" s="1"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>55192</v>
+      </c>
+      <c r="C266" s="1"/>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>54304</v>
+      </c>
+      <c r="C267" s="1"/>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>54898</v>
+      </c>
+      <c r="C268" s="1"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>54850</v>
+      </c>
+      <c r="C269" s="1"/>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>54781</v>
+      </c>
+      <c r="C270" s="1"/>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>54201</v>
+      </c>
+      <c r="C271" s="1"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>55935</v>
+      </c>
+      <c r="C272" s="1"/>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>55812</v>
+      </c>
+      <c r="C273" s="1"/>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>55779</v>
+      </c>
+      <c r="C274" s="1"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>55308</v>
+      </c>
+      <c r="C275" s="1"/>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>55766</v>
+      </c>
+      <c r="C276" s="1"/>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>56049</v>
+      </c>
+      <c r="C277" s="1"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>56050</v>
+      </c>
+      <c r="C278" s="1"/>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>55012</v>
+      </c>
+      <c r="C279" s="1"/>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>55504</v>
+      </c>
+      <c r="C280" s="1"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>55995</v>
+      </c>
+      <c r="C281" s="1"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>55639</v>
+      </c>
+      <c r="C282" s="1"/>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>53974</v>
+      </c>
+      <c r="C283" s="1"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>55732</v>
+      </c>
+      <c r="C284" s="1"/>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>55733</v>
+      </c>
+      <c r="C285" s="1"/>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>55734</v>
+      </c>
+      <c r="C286" s="1"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>55737</v>
+      </c>
+      <c r="C287" s="1"/>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>55558</v>
+      </c>
+      <c r="C288" s="1"/>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>55638</v>
+      </c>
+      <c r="C289" s="1"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>54922</v>
+      </c>
+      <c r="C290" s="1"/>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>55902</v>
+      </c>
+      <c r="C291" s="1"/>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>54968</v>
+      </c>
+      <c r="C292" s="1"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>54330</v>
+      </c>
+      <c r="C293" s="1"/>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>54072</v>
+      </c>
+      <c r="C294" s="1"/>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>54838</v>
+      </c>
+      <c r="C295" s="1"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>55258</v>
+      </c>
+      <c r="C296" s="1"/>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>53161</v>
+      </c>
+      <c r="C297" s="1"/>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>55716</v>
+      </c>
+      <c r="C298" s="1"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>55313</v>
+      </c>
+      <c r="C299" s="1"/>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>55312</v>
+      </c>
+      <c r="C300" s="1"/>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>56186</v>
+      </c>
+      <c r="C301" s="1"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>54783</v>
+      </c>
+      <c r="C302" s="1"/>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>54387</v>
+      </c>
+      <c r="C303" s="1"/>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>54621</v>
+      </c>
+      <c r="C304" s="1"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>54835</v>
+      </c>
+      <c r="C305" s="1"/>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>55253</v>
+      </c>
+      <c r="C306" s="1"/>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>55101</v>
+      </c>
+      <c r="C307" s="1"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>55395</v>
+      </c>
+      <c r="C308" s="1"/>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>54883</v>
+      </c>
+      <c r="C309" s="1"/>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>54312</v>
+      </c>
+      <c r="C310" s="1"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>54026</v>
+      </c>
+      <c r="C311" s="1"/>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>55865</v>
+      </c>
+      <c r="C312" s="1"/>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>55077</v>
+      </c>
+      <c r="C313" s="1"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>54851</v>
+      </c>
+      <c r="C314" s="1"/>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>55634</v>
+      </c>
+      <c r="C315" s="1"/>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>54229</v>
+      </c>
+      <c r="C316" s="1"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>54629</v>
+      </c>
+      <c r="C317" s="1"/>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>55793</v>
+      </c>
+      <c r="C318" s="1"/>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>54219</v>
+      </c>
+      <c r="C319" s="1"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>54539</v>
+      </c>
+      <c r="C320" s="1"/>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>55731</v>
+      </c>
+      <c r="C321" s="1"/>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>50390</v>
+      </c>
+      <c r="C322" s="1"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>50260</v>
+      </c>
+      <c r="C323" s="1"/>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>39469</v>
+      </c>
+      <c r="C324" s="1"/>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>45433</v>
+      </c>
+      <c r="C325" s="1"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>6976</v>
+      </c>
+      <c r="C326" s="1"/>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>49384</v>
+      </c>
+      <c r="C327" s="1"/>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>46562</v>
+      </c>
+      <c r="C328" s="1"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>38019</v>
+      </c>
+      <c r="C329" s="1"/>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>43494</v>
+      </c>
+      <c r="C330" s="1"/>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>49337</v>
+      </c>
+      <c r="C331" s="1"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>39013</v>
+      </c>
+      <c r="C332" s="1"/>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>23536</v>
+      </c>
+      <c r="C333" s="1"/>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>34684</v>
+      </c>
+      <c r="C334" s="1"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>35485</v>
+      </c>
+      <c r="C335" s="1"/>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>52067</v>
+      </c>
+      <c r="C336" s="1"/>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>46370</v>
+      </c>
+      <c r="C337" s="1"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>36096</v>
+      </c>
+      <c r="C338" s="1"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>36955</v>
+      </c>
+      <c r="C339" s="1"/>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>49903</v>
+      </c>
+      <c r="C340" s="1"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>51746</v>
+      </c>
+      <c r="C341" s="1"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>47603</v>
+      </c>
+      <c r="C342" s="1"/>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>53269</v>
+      </c>
+      <c r="C343" s="1"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344">
+        <v>52022</v>
+      </c>
+      <c r="C344" s="1"/>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>46790</v>
+      </c>
+      <c r="C345" s="1"/>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>53270</v>
+      </c>
+      <c r="C346" s="1"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>48917</v>
+      </c>
+      <c r="C347" s="1"/>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>35692</v>
+      </c>
+      <c r="C348" s="1"/>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>35691</v>
+      </c>
+      <c r="C349" s="1"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>34706</v>
+      </c>
+      <c r="C350" s="1"/>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>40541</v>
+      </c>
+      <c r="C351" s="1"/>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>46715</v>
+      </c>
+      <c r="C352" s="1"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>53708</v>
+      </c>
+      <c r="C353" s="1"/>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>51737</v>
+      </c>
+      <c r="C354" s="1"/>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>49239</v>
+      </c>
+      <c r="C355" s="1"/>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>31688</v>
+      </c>
+      <c r="C356" s="1"/>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>47593</v>
+      </c>
+      <c r="C357" s="1"/>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>51843</v>
+      </c>
+      <c r="C358" s="1"/>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>39262</v>
+      </c>
+      <c r="C359" s="1"/>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>39874</v>
+      </c>
+      <c r="C360" s="1"/>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>53381</v>
+      </c>
+      <c r="C361" s="1"/>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>22323</v>
+      </c>
+      <c r="C362" s="1"/>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>36684</v>
+      </c>
+      <c r="C363" s="1"/>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>41506</v>
+      </c>
+      <c r="C364" s="1"/>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>56195</v>
+      </c>
+      <c r="C365" s="1"/>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>53242</v>
+      </c>
+      <c r="C366" s="1"/>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>53028</v>
+      </c>
+      <c r="C367" s="1"/>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>53237</v>
+      </c>
+      <c r="C368" s="1"/>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>53792</v>
+      </c>
+      <c r="C369" s="1"/>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>55729</v>
+      </c>
+      <c r="C370" s="1"/>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>33943</v>
+      </c>
+      <c r="C371" s="1"/>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>32336</v>
+      </c>
+      <c r="C372" s="1"/>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>55378</v>
+      </c>
+      <c r="C373" s="1"/>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>35285</v>
+      </c>
+      <c r="C374" s="1"/>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>32759</v>
+      </c>
+      <c r="C375" s="1"/>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>8658</v>
+      </c>
+      <c r="C376" s="1"/>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>8188</v>
+      </c>
+      <c r="C377" s="1"/>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>54624</v>
+      </c>
+      <c r="C378" s="1"/>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379">
+        <v>53560</v>
+      </c>
+      <c r="C379" s="1"/>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>31258</v>
+      </c>
+      <c r="C380" s="1"/>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>31547</v>
+      </c>
+      <c r="C381" s="1"/>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>7679</v>
+      </c>
+      <c r="C382" s="1"/>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>2453</v>
+      </c>
+      <c r="C383" s="1"/>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>38112</v>
+      </c>
+      <c r="C384" s="1"/>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>54440</v>
+      </c>
+      <c r="C385" s="1"/>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>54173</v>
+      </c>
+      <c r="C386" s="1"/>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>9074</v>
+      </c>
+      <c r="C387" s="1"/>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>13332</v>
+      </c>
+      <c r="C388" s="1"/>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>56196</v>
+      </c>
+      <c r="C389" s="1"/>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390">
+        <v>43180</v>
+      </c>
+      <c r="C390" s="1"/>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>43181</v>
+      </c>
+      <c r="C391" s="1"/>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>9078</v>
+      </c>
+      <c r="C392" s="1"/>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>24750</v>
+      </c>
+      <c r="C393" s="1"/>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>24748</v>
+      </c>
+      <c r="C394" s="1"/>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>52756</v>
+      </c>
+      <c r="C395" s="1"/>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>53874</v>
+      </c>
+      <c r="C396" s="1"/>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>21651</v>
+      </c>
+      <c r="C397" s="1"/>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>51189</v>
+      </c>
+      <c r="C398" s="1"/>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>48805</v>
+      </c>
+      <c r="C399" s="1"/>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>6829</v>
+      </c>
+      <c r="C400" s="1"/>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>24870</v>
+      </c>
+      <c r="C401" s="1"/>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>2451</v>
+      </c>
+      <c r="C402" s="1"/>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>24786</v>
+      </c>
+      <c r="C403" s="1"/>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>9975</v>
+      </c>
+      <c r="C404" s="1"/>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>13334</v>
+      </c>
+      <c r="C405" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{96B45C00-1EB9-4D5E-B0AF-408718919FAD}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{1BB9B4E4-5BA4-4817-95BE-1861DDEF59AB}"/>
     <hyperlink ref="C4" r:id="rId3" xr:uid="{3D4ADFD1-3E3E-419E-B2ED-C8A4A6C4EADD}"/>
     <hyperlink ref="C5" r:id="rId4" xr:uid="{03710971-770F-4139-BB18-5B811FB2C21B}"/>
+    <hyperlink ref="C65" r:id="rId5" xr:uid="{7669169B-8E5B-4C38-8E5F-7626A00EEEA8}"/>
+    <hyperlink ref="C81" r:id="rId6" xr:uid="{B61906DA-BC73-4354-BE7F-2E8A597EAE73}"/>
+    <hyperlink ref="C96" r:id="rId7" xr:uid="{D8E725F8-C6D0-471C-907F-FE748108D467}"/>
+    <hyperlink ref="C99" r:id="rId8" xr:uid="{F0BD9B04-2BBD-4EB5-B9B9-B915DBE891CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>